--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29910"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Laptop\e\VVSS\CamiVVSS_ro2025-2026\Labs\CheckListsAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE83867-3721-469D-B0A3-67FDA22FF09F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="13_ncr:1_{EFE83867-3721-469D-B0A3-67FDA22FF09F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D56FFB0-A547-4ED8-AC29-34132A9A46AE}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,8 +18,11 @@
     <sheet name="Coding Phase Defects" sheetId="5" r:id="rId3"/>
     <sheet name="Tool-basedCodeAnalysis" sheetId="8" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -36,20 +39,53 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="75">
+  <si>
+    <t>do not print this form</t>
+  </si>
+  <si>
+    <t>Echipa</t>
+  </si>
+  <si>
+    <t>Review Form. Requirements Defects</t>
+  </si>
+  <si>
+    <t>Numele si prenumele</t>
+  </si>
+  <si>
+    <t>Grupa</t>
+  </si>
+  <si>
+    <t>Student 1:</t>
+  </si>
+  <si>
+    <t>Zdroba Alexandru</t>
+  </si>
   <si>
     <t>Document  Title:</t>
   </si>
   <si>
+    <t>Requirements Document</t>
+  </si>
+  <si>
+    <t>Student 2:</t>
+  </si>
+  <si>
+    <t>Author Name:</t>
+  </si>
+  <si>
+    <t>Firicescu George</t>
+  </si>
+  <si>
+    <t>Student 3:</t>
+  </si>
+  <si>
+    <t>Reviewer Name:</t>
+  </si>
+  <si>
     <t xml:space="preserve">Review date: </t>
   </si>
   <si>
-    <t>Reviewer Name:</t>
-  </si>
-  <si>
-    <t>do not print this form</t>
-  </si>
-  <si>
     <t>Crt. No.</t>
   </si>
   <si>
@@ -62,76 +98,213 @@
     <t>Comments/ improvements</t>
   </si>
   <si>
+    <t>R01</t>
+  </si>
+  <si>
+    <t>fr8</t>
+  </si>
+  <si>
+    <t>Nu este mentionat exact despre ce total este vorba (total incasari, incasari - cheltuieli).</t>
+  </si>
+  <si>
+    <t>fr1/fr4</t>
+  </si>
+  <si>
+    <t>Nu sunt specificate operatiile de gestiune pentru ingrediente.</t>
+  </si>
+  <si>
+    <t>R02</t>
+  </si>
+  <si>
+    <t>fr6</t>
+  </si>
+  <si>
+    <t>Nu se specifica scenariul in care un client doreste modificarea retetei/ sau doreste extra ingrediente.</t>
+  </si>
+  <si>
+    <t>R03</t>
+  </si>
+  <si>
+    <t>fr3</t>
+  </si>
+  <si>
+    <t>Orice utilizator poate modifica produsele, in loc sa fie utilizatori cu permisiuni reduse si administratori.</t>
+  </si>
+  <si>
+    <t>Aplicatia nu mentioneaza lista de alergeni pentru fiecare produs, sau ingredientele care pot interfera cu anumite restrictii.</t>
+  </si>
+  <si>
     <t>Effort to review document (hours):</t>
   </si>
   <si>
-    <t>Author Name:</t>
+    <t>Review Form. Architectural Design Defects</t>
+  </si>
+  <si>
+    <t>Architectural Design Document</t>
   </si>
   <si>
     <t xml:space="preserve">Author Name: </t>
   </si>
   <si>
+    <t>Georgescu Anca</t>
+  </si>
+  <si>
+    <t>A01</t>
+  </si>
+  <si>
+    <t>src/main/java/drinkshop/</t>
+  </si>
+  <si>
+    <t>YES - Structură 5-tier clară: domain → repository → service → ui + utilities (validator, export, reports)</t>
+  </si>
+  <si>
+    <r>
+      <t>A02</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF928374"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>pom.xml, src/ structure</t>
+  </si>
+  <si>
+    <t>YES - Layering bine definit: domain (entities), repository (persistence), service (business logic), ui (presentation)</t>
+  </si>
+  <si>
+    <t>A03</t>
+  </si>
+  <si>
+    <t>DrinkShopService.java</t>
+  </si>
+  <si>
+    <r>
+      <t>PARTIAL - Acoperite: produse (1), tip+categorie (2), rețete cu ingrediente (4), stocuri (5), comenzi (6), rapoarte zilnice (8). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF928374"/>
+        <rFont val="Segoe WPC"/>
+        <charset val="1"/>
+      </rPr>
+      <t>LIPSĂ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF928374"/>
+        <rFont val="Segoe WPC"/>
+        <charset val="1"/>
+      </rPr>
+      <t>: Cerința 3 - Gestiunea tipurilor și categoriilor ca entități independente (add/delete TipBautura și CategorieBautura nu au service propriu)</t>
+    </r>
+  </si>
+  <si>
+    <t>A04</t>
+  </si>
+  <si>
+    <t>service/*.java</t>
+  </si>
+  <si>
+    <t>YES - Fiecare Service are clase domeniu și validatori: ProductService+Product, OrderService+Order, etc.</t>
+  </si>
+  <si>
+    <t>A05</t>
+  </si>
+  <si>
+    <t>service/validator/ValidationException.java</t>
+  </si>
+  <si>
+    <t>PARTIAL - Exception handling doar în validators; lipsesc try-catch în services și UI controllers</t>
+  </si>
+  <si>
+    <t>A06</t>
+  </si>
+  <si>
+    <t>repository/AbstractRepository.java</t>
+  </si>
+  <si>
+    <t>YES - Repository Pattern (AbstractRepository), Service Layer Pattern, Validator Pattern clar implementate</t>
+  </si>
+  <si>
+    <t>A07</t>
+  </si>
+  <si>
+    <t>domain/, service/, repository/</t>
+  </si>
+  <si>
+    <t>YES - Nume descriptive și sugestive: FileProductRepository, OrderValidator, DailyReportService</t>
+  </si>
+  <si>
+    <t>A08</t>
+  </si>
+  <si>
+    <t>YES - SRP respectat: fiecare clasă are o singură responsabilitate bine definită</t>
+  </si>
+  <si>
+    <t>A09</t>
+  </si>
+  <si>
+    <t>, Reteta.java</t>
+  </si>
+  <si>
+    <t>YES - Relații semantice clare: Order→OrderItems, Reteta→IngredientReteta, Product→Categorie</t>
+  </si>
+  <si>
+    <r>
+      <t>A10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF928374"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>domain/*.java</t>
+  </si>
+  <si>
+    <t>PARTIAL - Entități principale prezente (Product, Order, Reteta, Stoc), dar lipsă entități pentru TipBautura și CategorieBautura (sunt enum-uri, nu clase). Relații: ok pentru comenzi și rețete, dar tipuri/categorii nu sunt tratate ca entități persistente</t>
+  </si>
+  <si>
+    <t>Review Form. Coding Defects</t>
+  </si>
+  <si>
+    <t>Coding Document</t>
+  </si>
+  <si>
     <t>Popescu Ionel</t>
   </si>
   <si>
-    <t>Georgescu Anca</t>
-  </si>
-  <si>
-    <t>Firicescu George</t>
-  </si>
-  <si>
-    <t>Requirements Document</t>
-  </si>
-  <si>
-    <t>Architectural Design Document</t>
-  </si>
-  <si>
-    <t>Coding Document</t>
-  </si>
-  <si>
-    <t>Review Form. Coding Defects</t>
-  </si>
-  <si>
-    <t>Review Form. Architectural Design Defects</t>
-  </si>
-  <si>
-    <t>Review Form. Requirements Defects</t>
-  </si>
-  <si>
-    <t>Student 1:</t>
-  </si>
-  <si>
-    <t>Student 2:</t>
-  </si>
-  <si>
-    <t>Student 3:</t>
-  </si>
-  <si>
-    <t>Echipa</t>
-  </si>
-  <si>
-    <t>Grupa</t>
+    <t>Tool-based Code Analysis</t>
   </si>
   <si>
     <t>Tool used:</t>
   </si>
   <si>
+    <t>File, Line</t>
+  </si>
+  <si>
+    <t>Issue</t>
+  </si>
+  <si>
     <t>Before</t>
   </si>
   <si>
-    <t>Issue</t>
-  </si>
-  <si>
-    <t>File, Line</t>
-  </si>
-  <si>
     <t>After/Argument</t>
-  </si>
-  <si>
-    <t>Numele si prenumele</t>
-  </si>
-  <si>
-    <t>Tool-based Code Analysis</t>
   </si>
   <si>
     <t>Effort to perform tool-based code analysis (hours):</t>
@@ -141,34 +314,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -226,6 +378,44 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF928374"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF928374"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF928374"/>
+      <name val="Segoe WPC"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -253,7 +443,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -322,82 +512,108 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -707,172 +923,288 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="6"/>
-    <col min="2" max="2" width="12.26953125" style="6" customWidth="1"/>
-    <col min="3" max="4" width="16.26953125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.453125" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.90625" style="6"/>
-    <col min="9" max="9" width="21" style="6" customWidth="1"/>
-    <col min="10" max="10" width="14.453125" style="6" customWidth="1"/>
-    <col min="11" max="16384" width="8.90625" style="6"/>
+    <col min="1" max="1" width="8.85546875" style="5"/>
+    <col min="2" max="2" width="12.28515625" style="5" customWidth="1"/>
+    <col min="3" max="4" width="16.28515625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="41.42578125" style="5" customWidth="1"/>
+    <col min="6" max="8" width="8.85546875" style="5"/>
+    <col min="9" max="9" width="21" style="5" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="5" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="4"/>
-      <c r="B1" s="5" t="s">
+    <row r="1" spans="1:10" ht="15.6">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="16"/>
+      <c r="B2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B2" s="24" t="s">
+      <c r="J2" s="39" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="39">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="19"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="21"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="39"/>
+      <c r="J5" s="39"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="16"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="16"/>
+      <c r="B9" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+    </row>
+    <row r="10" spans="1:10" ht="30.75">
+      <c r="A10" s="16"/>
+      <c r="B10" s="39">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="H3" s="17" t="s">
+      <c r="D10" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C4" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="25"/>
-      <c r="H4" s="17" t="s">
+      <c r="E10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C5" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="27"/>
-      <c r="H5" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B6" s="8"/>
-      <c r="C6" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C7" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B9" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B10" s="3">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B11" s="3">
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+    </row>
+    <row r="11" spans="1:10" ht="30.75">
+      <c r="A11" s="16"/>
+      <c r="B11" s="39">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B12" s="3">
+      <c r="C11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+    </row>
+    <row r="12" spans="1:10" ht="45.75">
+      <c r="A12" s="16"/>
+      <c r="B12" s="39">
         <f t="shared" ref="B12:B25" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B13" s="3">
+      <c r="C12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+    </row>
+    <row r="13" spans="1:10" ht="45.75">
+      <c r="A13" s="16"/>
+      <c r="B13" s="39">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B14" s="3">
+      <c r="C13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+    </row>
+    <row r="14" spans="1:10" ht="45.75">
+      <c r="A14" s="16"/>
+      <c r="B14" s="39">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="1"/>
+      <c r="C14" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="D14" s="1"/>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B15" s="3">
+      <c r="E14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="16"/>
+      <c r="B15" s="39">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B16" s="3">
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="16"/>
+      <c r="B16" s="39">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B17" s="3">
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17" s="39">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -880,84 +1212,87 @@
       <c r="D17" s="1"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B18" s="3">
+    <row r="18" spans="2:5">
+      <c r="B18" s="39">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="15"/>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B19" s="3">
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="40"/>
+    </row>
+    <row r="19" spans="2:5">
+      <c r="B19" s="39">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="15"/>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B20" s="3">
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="40"/>
+    </row>
+    <row r="20" spans="2:5">
+      <c r="B20" s="39">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="15"/>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B21" s="3">
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="40"/>
+    </row>
+    <row r="21" spans="2:5">
+      <c r="B21" s="39">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="15"/>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B22" s="3">
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="40"/>
+    </row>
+    <row r="22" spans="2:5">
+      <c r="B22" s="39">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="15"/>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B23" s="3">
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="40"/>
+    </row>
+    <row r="23" spans="2:5">
+      <c r="B23" s="39">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="15"/>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B24" s="3">
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="40"/>
+    </row>
+    <row r="24" spans="2:5">
+      <c r="B24" s="39">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="15"/>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B25" s="3">
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="40"/>
+    </row>
+    <row r="25" spans="2:5">
+      <c r="B25" s="39">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="15"/>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="C27" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="12"/>
-      <c r="E27" s="1"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="40"/>
+    </row>
+    <row r="27" spans="2:5">
+      <c r="B27" s="16"/>
+      <c r="C27" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" s="11"/>
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -979,207 +1314,342 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J28"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="6"/>
-    <col min="2" max="2" width="12.26953125" style="6" customWidth="1"/>
-    <col min="3" max="4" width="16.26953125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.453125" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.90625" style="6"/>
-    <col min="9" max="9" width="22.08984375" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.90625" style="6"/>
+    <col min="1" max="1" width="8.85546875" style="5"/>
+    <col min="2" max="2" width="12.28515625" style="5" customWidth="1"/>
+    <col min="3" max="4" width="16.28515625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="41.42578125" style="5" customWidth="1"/>
+    <col min="6" max="8" width="8.85546875" style="5"/>
+    <col min="9" max="9" width="22.140625" style="5" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="4"/>
-      <c r="B1" s="5" t="s">
+    <row r="1" spans="1:10" ht="15.6">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="16"/>
+      <c r="B2" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B2" s="24" t="s">
+      <c r="J2" s="39" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="22"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="24"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="39"/>
+      <c r="J5" s="39"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="16"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="16"/>
+      <c r="B9" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="H3" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C4" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="28"/>
-      <c r="H4" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C5" s="7" t="s">
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+    </row>
+    <row r="10" spans="1:10" ht="43.5">
+      <c r="A10" s="16"/>
+      <c r="B10" s="32">
+        <v>1</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+    </row>
+    <row r="11" spans="1:10" ht="43.5">
+      <c r="A11" s="16"/>
+      <c r="B11" s="34">
+        <v>2</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+    </row>
+    <row r="12" spans="1:10" ht="83.25">
+      <c r="A12" s="16"/>
+      <c r="B12" s="34">
+        <v>3</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+    </row>
+    <row r="13" spans="1:10" ht="43.5">
+      <c r="A13" s="16"/>
+      <c r="B13" s="34">
+        <v>4</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+    </row>
+    <row r="14" spans="1:10" ht="43.5">
+      <c r="A14" s="16"/>
+      <c r="B14" s="34">
+        <v>5</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+    </row>
+    <row r="15" spans="1:10" ht="43.5">
+      <c r="A15" s="16"/>
+      <c r="B15" s="34">
+        <v>6</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+    </row>
+    <row r="16" spans="1:10" ht="43.5">
+      <c r="A16" s="16"/>
+      <c r="B16" s="34">
+        <v>7</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+    </row>
+    <row r="17" spans="2:5" ht="29.25">
+      <c r="B17" s="34">
+        <v>8</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="35" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="29.25">
+      <c r="B18" s="34">
+        <v>9</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="35" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="83.25">
+      <c r="B19" s="34">
         <v>10</v>
       </c>
-      <c r="D5" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="30"/>
-      <c r="H5" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B6" s="8"/>
-      <c r="C6" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C7" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B9" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B10" s="3">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B11" s="3">
-        <f>B10+1</f>
-        <v>2</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B12" s="3">
-        <f t="shared" ref="B12:B26" si="0">B11+1</f>
-        <v>3</v>
-      </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B13" s="3">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B14" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B15" s="3">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B16" s="3">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B17" s="3">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B18" s="3">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B19" s="3">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B20" s="3">
-        <f t="shared" si="0"/>
+      <c r="C19" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" s="37" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5">
+      <c r="B20" s="39">
+        <f t="shared" ref="B12:B26" si="0">B19+1</f>
         <v>11</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B21" s="3">
+    <row r="21" spans="2:5">
+      <c r="B21" s="39">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -1187,8 +1657,8 @@
       <c r="D21" s="1"/>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B22" s="3">
+    <row r="22" spans="2:5">
+      <c r="B22" s="39">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
@@ -1196,8 +1666,8 @@
       <c r="D22" s="1"/>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B23" s="3">
+    <row r="23" spans="2:5">
+      <c r="B23" s="39">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -1205,8 +1675,8 @@
       <c r="D23" s="1"/>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B24" s="3">
+    <row r="24" spans="2:5">
+      <c r="B24" s="39">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -1214,8 +1684,8 @@
       <c r="D24" s="1"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B25" s="3">
+    <row r="25" spans="2:5">
+      <c r="B25" s="39">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -1223,8 +1693,8 @@
       <c r="D25" s="1"/>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B26" s="3">
+    <row r="26" spans="2:5">
+      <c r="B26" s="39">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
@@ -1232,11 +1702,18 @@
       <c r="D26" s="1"/>
       <c r="E26" s="2"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="C28" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="12"/>
+    <row r="27" spans="2:5" ht="15">
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="31"/>
+    </row>
+    <row r="28" spans="2:5">
+      <c r="B28" s="16"/>
+      <c r="C28" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" s="11"/>
       <c r="E28" s="1"/>
     </row>
   </sheetData>
@@ -1259,172 +1736,256 @@
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="6"/>
-    <col min="2" max="2" width="12.26953125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16.26953125" style="6" customWidth="1"/>
-    <col min="4" max="4" width="18" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.453125" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.90625" style="6"/>
-    <col min="9" max="9" width="26.7265625" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.90625" style="6"/>
+    <col min="1" max="1" width="8.85546875" style="5"/>
+    <col min="2" max="2" width="12.28515625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="18" style="5" customWidth="1"/>
+    <col min="5" max="5" width="41.42578125" style="5" customWidth="1"/>
+    <col min="6" max="8" width="8.85546875" style="5"/>
+    <col min="9" max="9" width="26.7109375" style="5" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="4"/>
-      <c r="B1" s="5" t="s">
+    <row r="1" spans="1:10" ht="15.6">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="16"/>
+      <c r="B2" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B2" s="24" t="s">
+      <c r="J2" s="39" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" s="25"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="27"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="39"/>
+      <c r="J5" s="39"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="16"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="16"/>
+      <c r="B9" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="H3" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C4" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="31"/>
-      <c r="H4" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C5" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="33"/>
-      <c r="H5" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B6" s="8"/>
-      <c r="C6" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C7" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B9" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B10" s="3">
+      <c r="E9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="16"/>
+      <c r="B10" s="39">
         <v>1</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B11" s="3">
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="16"/>
+      <c r="B11" s="39">
         <f>B10+1</f>
         <v>2</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B12" s="3">
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="16"/>
+      <c r="B12" s="39">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B13" s="3">
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="16"/>
+      <c r="B13" s="39">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B14" s="3">
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="16"/>
+      <c r="B14" s="39">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B15" s="3">
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="16"/>
+      <c r="B15" s="39">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B16" s="3">
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="16"/>
+      <c r="B16" s="39">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B17" s="3">
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17" s="39">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -1432,8 +1993,8 @@
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B18" s="3">
+    <row r="18" spans="2:5">
+      <c r="B18" s="39">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -1441,8 +2002,8 @@
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B19" s="3">
+    <row r="19" spans="2:5">
+      <c r="B19" s="39">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -1450,8 +2011,8 @@
       <c r="D19" s="1"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B20" s="3">
+    <row r="20" spans="2:5">
+      <c r="B20" s="39">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -1459,8 +2020,8 @@
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B21" s="3">
+    <row r="21" spans="2:5">
+      <c r="B21" s="39">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -1468,8 +2029,8 @@
       <c r="D21" s="1"/>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B22" s="3">
+    <row r="22" spans="2:5">
+      <c r="B22" s="39">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
@@ -1477,8 +2038,8 @@
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B23" s="3">
+    <row r="23" spans="2:5">
+      <c r="B23" s="39">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -1486,8 +2047,8 @@
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B24" s="3">
+    <row r="24" spans="2:5">
+      <c r="B24" s="39">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -1495,8 +2056,8 @@
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B25" s="3">
+    <row r="25" spans="2:5">
+      <c r="B25" s="39">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -1504,8 +2065,8 @@
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B26" s="3">
+    <row r="26" spans="2:5">
+      <c r="B26" s="39">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
@@ -1513,8 +2074,8 @@
       <c r="D26" s="1"/>
       <c r="E26" s="2"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B27" s="3">
+    <row r="27" spans="2:5">
+      <c r="B27" s="39">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
@@ -1522,8 +2083,8 @@
       <c r="D27" s="2"/>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B28" s="3">
+    <row r="28" spans="2:5">
+      <c r="B28" s="39">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
@@ -1531,8 +2092,8 @@
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B29" s="3">
+    <row r="29" spans="2:5">
+      <c r="B29" s="39">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -1540,8 +2101,8 @@
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B30" s="3">
+    <row r="30" spans="2:5">
+      <c r="B30" s="39">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
@@ -1549,11 +2110,12 @@
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="C32" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="12"/>
+    <row r="32" spans="2:5">
+      <c r="B32" s="16"/>
+      <c r="C32" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" s="11"/>
       <c r="E32" s="1"/>
     </row>
   </sheetData>
@@ -1576,113 +2138,152 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:J35"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="6"/>
-    <col min="2" max="2" width="12.26953125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16.26953125" style="6" customWidth="1"/>
-    <col min="4" max="4" width="18" style="6" customWidth="1"/>
-    <col min="5" max="5" width="23.90625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="16.6328125" style="6" customWidth="1"/>
-    <col min="7" max="8" width="8.90625" style="6"/>
-    <col min="9" max="9" width="26.7265625" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.90625" style="6"/>
+    <col min="1" max="1" width="8.85546875" style="5"/>
+    <col min="2" max="2" width="12.28515625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="18" style="5" customWidth="1"/>
+    <col min="5" max="5" width="23.85546875" style="5" customWidth="1"/>
+    <col min="6" max="6" width="16.5703125" style="5" customWidth="1"/>
+    <col min="7" max="8" width="8.85546875" style="5"/>
+    <col min="9" max="9" width="26.7109375" style="5" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="4"/>
-      <c r="B1" s="5" t="s">
+    <row r="1" spans="1:10" ht="15.6">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="16"/>
+      <c r="B2" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B2" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="H3" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C4" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="H4" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C5" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="H5" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B6" s="8"/>
-      <c r="C6" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="20"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B9" s="10" t="s">
+      <c r="J2" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B10" s="3">
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="39"/>
+      <c r="J5" s="39"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="16"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="16"/>
+      <c r="B9" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="16"/>
+      <c r="B10" s="39">
         <v>1</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B11" s="3">
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="16"/>
+      <c r="B11" s="39">
         <f>B10+1</f>
         <v>2</v>
       </c>
@@ -1690,9 +2291,14 @@
       <c r="D11" s="1"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B12" s="3">
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="16"/>
+      <c r="B12" s="39">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
       </c>
@@ -1700,9 +2306,14 @@
       <c r="D12" s="1"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B13" s="3">
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="16"/>
+      <c r="B13" s="39">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1710,9 +2321,14 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B14" s="3">
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="16"/>
+      <c r="B14" s="39">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -1720,9 +2336,14 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B15" s="3">
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="16"/>
+      <c r="B15" s="39">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -1730,9 +2351,14 @@
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B16" s="3">
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="16"/>
+      <c r="B16" s="39">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -1740,9 +2366,13 @@
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B17" s="3">
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" s="39">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -1751,8 +2381,8 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B18" s="3">
+    <row r="18" spans="2:6">
+      <c r="B18" s="39">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -1761,8 +2391,8 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B19" s="3">
+    <row r="19" spans="2:6">
+      <c r="B19" s="39">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -1771,8 +2401,8 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B20" s="3">
+    <row r="20" spans="2:6">
+      <c r="B20" s="39">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -1781,8 +2411,8 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B21" s="3">
+    <row r="21" spans="2:6">
+      <c r="B21" s="39">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -1791,8 +2421,8 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B22" s="3">
+    <row r="22" spans="2:6">
+      <c r="B22" s="39">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
@@ -1801,8 +2431,8 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B23" s="3">
+    <row r="23" spans="2:6">
+      <c r="B23" s="39">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -1811,8 +2441,8 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B24" s="3">
+    <row r="24" spans="2:6">
+      <c r="B24" s="39">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -1821,8 +2451,8 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="3">
+    <row r="25" spans="2:6">
+      <c r="B25" s="39">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -1831,8 +2461,8 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B26" s="3">
+    <row r="26" spans="2:6">
+      <c r="B26" s="39">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
@@ -1841,8 +2471,8 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B27" s="3">
+    <row r="27" spans="2:6">
+      <c r="B27" s="39">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
@@ -1851,8 +2481,8 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B28" s="3">
+    <row r="28" spans="2:6">
+      <c r="B28" s="39">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
@@ -1861,8 +2491,8 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B29" s="3">
+    <row r="29" spans="2:6">
+      <c r="B29" s="39">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -1871,8 +2501,8 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B30" s="3">
+    <row r="30" spans="2:6">
+      <c r="B30" s="39">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
@@ -1881,16 +2511,17 @@
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="C32" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="18"/>
-    </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F35" s="21"/>
+    <row r="32" spans="2:6">
+      <c r="B32" s="16"/>
+      <c r="C32" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="15"/>
+    </row>
+    <row r="35" spans="6:6">
+      <c r="F35" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Laptop\e\VVSS\CamiVVSS_ro2025-2026\Labs\CheckListsAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="13_ncr:1_{EFE83867-3721-469D-B0A3-67FDA22FF09F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D56FFB0-A547-4ED8-AC29-34132A9A46AE}"/>
+  <xr:revisionPtr revIDLastSave="122" documentId="13_ncr:1_{EFE83867-3721-469D-B0A3-67FDA22FF09F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAD67BE2-A3EB-49C8-95C1-F2675151D60C}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="650" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="95">
   <si>
     <t>do not print this form</t>
   </si>
@@ -71,6 +71,9 @@
     <t>Student 2:</t>
   </si>
   <si>
+    <t>Vitelaru Teodor</t>
+  </si>
+  <si>
     <t>Author Name:</t>
   </si>
   <si>
@@ -80,10 +83,16 @@
     <t>Student 3:</t>
   </si>
   <si>
+    <t>Ursoiu Calin</t>
+  </si>
+  <si>
     <t>Reviewer Name:</t>
   </si>
   <si>
     <t xml:space="preserve">Review date: </t>
+  </si>
+  <si>
+    <t>14/03/2026</t>
   </si>
   <si>
     <t>Crt. No.</t>
@@ -295,6 +304,9 @@
     <t>Tool used:</t>
   </si>
   <si>
+    <t>SonarQube</t>
+  </si>
+  <si>
     <t>File, Line</t>
   </si>
   <si>
@@ -307,7 +319,72 @@
     <t>After/Argument</t>
   </si>
   <si>
-    <t>Effort to perform tool-based code analysis (hours):</t>
+    <t>AbstractRepository.java:37</t>
+  </si>
+  <si>
+    <t>Metoda de save e identica cu cea de update.</t>
+  </si>
+  <si>
+    <t>AbstractRepository.java:20</t>
+  </si>
+  <si>
+    <t>Un cast redundant.</t>
+  </si>
+  <si>
+    <t>return (List&lt;E&gt;)StreamSupport.stream(entities.values().spliterator(), false).toList();
+//                    .collect(Collectors.toList());</t>
+  </si>
+  <si>
+    <t>return StreamSupport.stream(entities.values().spliterator(),</t>
+  </si>
+  <si>
+    <t>DailyReportService.java:21</t>
+  </si>
+  <si>
+    <t>Instructiuni comentate si nefolosite,</t>
+  </si>
+  <si>
+    <t>List&lt;Order&gt; orders = StreamSupport.stream(repo.findAll().spliterator(), false)
+//                .collect(Collectors.toList());
+        return repo.findAll().size();</t>
+  </si>
+  <si>
+    <t>public int getTotalOrders() {
+        return repo.findAll().size();
+    }</t>
+  </si>
+  <si>
+    <t>DailyReportService.java:6</t>
+  </si>
+  <si>
+    <t>Importuri nefolosite</t>
+  </si>
+  <si>
+    <t>import java.util.List;
+import java.util.stream.Collectors;
+import java.util.stream.StreamSupport;</t>
+  </si>
+  <si>
+    <t>ProductService.java:31</t>
+  </si>
+  <si>
+    <t>public List&lt;Product&gt; getAllProducts() {
+//        Iterable&lt;Product&gt; it=productRepo.findAll();
+//        ArrayList&lt;Product&gt; products=new ArrayList&lt;&gt;();
+//        it.forEach(products::add);
+//        return products;
+//        return StreamSupport.stream(productRepo.findAll().spliterator(), false)
+//                    .collect(Collectors.toList());
+        return productRepo.findAll();
+    }</t>
+  </si>
+  <si>
+    <t>public List&lt;Product&gt; getAllProducts() {
+        return productRepo.findAll();
+    }</t>
+  </si>
+  <si>
+    <t>Effort to perform tool-based code analysis (hours): 1</t>
   </si>
 </sst>
 </file>
@@ -553,8 +630,30 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -592,28 +691,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -630,6 +709,105 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1495425</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDF62A12-D8BF-92C4-35A8-242D63CBD52F}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{1162A5B0-8584-104B-FFAF-5164C083838B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3695700" y="1638300"/>
+          <a:ext cx="1495425" cy="676275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75354AD8-110C-1EF9-71BF-74138A2AF792}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{BDF62A12-D8BF-92C4-35A8-242D63CBD52F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5286375" y="1638300"/>
+          <a:ext cx="1323975" cy="685800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -945,27 +1123,27 @@
       <c r="E1" s="16"/>
       <c r="F1" s="16"/>
       <c r="G1" s="16"/>
-      <c r="H1" s="38" t="s">
+      <c r="H1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="16"/>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
       <c r="F2" s="16"/>
       <c r="G2" s="16"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39" t="s">
+      <c r="H2" s="24"/>
+      <c r="I2" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="39" t="s">
+      <c r="J2" s="24" t="s">
         <v>4</v>
       </c>
     </row>
@@ -977,13 +1155,13 @@
       <c r="E3" s="16"/>
       <c r="F3" s="16"/>
       <c r="G3" s="16"/>
-      <c r="H3" s="39" t="s">
+      <c r="H3" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="39" t="s">
+      <c r="I3" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="39">
+      <c r="J3" s="24">
         <v>237</v>
       </c>
     </row>
@@ -993,44 +1171,54 @@
       <c r="C4" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="19"/>
+      <c r="E4" s="29"/>
       <c r="F4" s="16"/>
       <c r="G4" s="16"/>
-      <c r="H4" s="39" t="s">
+      <c r="H4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
+      <c r="I4" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="24">
+        <v>237</v>
+      </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="16"/>
       <c r="B5" s="16"/>
       <c r="C5" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="21"/>
+      <c r="D5" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="31"/>
       <c r="F5" s="16"/>
       <c r="G5" s="16"/>
-      <c r="H5" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39"/>
+      <c r="H5" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="24">
+        <v>237</v>
+      </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="16"/>
       <c r="B6" s="7"/>
       <c r="C6" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
+        <v>15</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="26"/>
       <c r="F6" s="16"/>
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
@@ -1041,10 +1229,12 @@
       <c r="A7" s="16"/>
       <c r="B7" s="16"/>
       <c r="C7" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
+        <v>16</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="26"/>
       <c r="F7" s="16"/>
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
@@ -1054,16 +1244,16 @@
     <row r="9" spans="1:10">
       <c r="A9" s="16"/>
       <c r="B9" s="9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F9" s="16"/>
       <c r="G9" s="16"/>
@@ -1073,17 +1263,17 @@
     </row>
     <row r="10" spans="1:10" ht="30.75">
       <c r="A10" s="16"/>
-      <c r="B10" s="39">
+      <c r="B10" s="24">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F10" s="16"/>
       <c r="G10" s="16"/>
@@ -1093,18 +1283,18 @@
     </row>
     <row r="11" spans="1:10" ht="30.75">
       <c r="A11" s="16"/>
-      <c r="B11" s="39">
+      <c r="B11" s="24">
         <f>B10+1</f>
         <v>2</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F11" s="16"/>
       <c r="G11" s="16"/>
@@ -1114,18 +1304,18 @@
     </row>
     <row r="12" spans="1:10" ht="45.75">
       <c r="A12" s="16"/>
-      <c r="B12" s="39">
+      <c r="B12" s="24">
         <f t="shared" ref="B12:B25" si="0">B11+1</f>
         <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F12" s="16"/>
       <c r="G12" s="16"/>
@@ -1135,18 +1325,18 @@
     </row>
     <row r="13" spans="1:10" ht="45.75">
       <c r="A13" s="16"/>
-      <c r="B13" s="39">
+      <c r="B13" s="24">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F13" s="16"/>
       <c r="G13" s="16"/>
@@ -1156,16 +1346,16 @@
     </row>
     <row r="14" spans="1:10" ht="45.75">
       <c r="A14" s="16"/>
-      <c r="B14" s="39">
+      <c r="B14" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F14" s="16"/>
       <c r="G14" s="16"/>
@@ -1175,7 +1365,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="16"/>
-      <c r="B15" s="39">
+      <c r="B15" s="24">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -1190,7 +1380,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="16"/>
-      <c r="B16" s="39">
+      <c r="B16" s="24">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -1204,7 +1394,7 @@
       <c r="J16" s="16"/>
     </row>
     <row r="17" spans="2:5">
-      <c r="B17" s="39">
+      <c r="B17" s="24">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -1213,81 +1403,81 @@
       <c r="E17" s="2"/>
     </row>
     <row r="18" spans="2:5">
-      <c r="B18" s="39">
+      <c r="B18" s="24">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="40"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="25"/>
     </row>
     <row r="19" spans="2:5">
-      <c r="B19" s="39">
+      <c r="B19" s="24">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="40"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="25"/>
     </row>
     <row r="20" spans="2:5">
-      <c r="B20" s="39">
+      <c r="B20" s="24">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="39"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="40"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="25"/>
     </row>
     <row r="21" spans="2:5">
-      <c r="B21" s="39">
+      <c r="B21" s="24">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="39"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="40"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="25"/>
     </row>
     <row r="22" spans="2:5">
-      <c r="B22" s="39">
+      <c r="B22" s="24">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="39"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="40"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="25"/>
     </row>
     <row r="23" spans="2:5">
-      <c r="B23" s="39">
+      <c r="B23" s="24">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="39"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="40"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="25"/>
     </row>
     <row r="24" spans="2:5">
-      <c r="B24" s="39">
+      <c r="B24" s="24">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="40"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="25"/>
     </row>
     <row r="25" spans="2:5">
-      <c r="B25" s="39">
+      <c r="B25" s="24">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="40"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="25"/>
     </row>
     <row r="27" spans="2:5">
       <c r="B27" s="16"/>
       <c r="C27" s="10" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D27" s="11"/>
       <c r="E27" s="1">
@@ -1335,27 +1525,27 @@
       <c r="E1" s="16"/>
       <c r="F1" s="16"/>
       <c r="G1" s="16"/>
-      <c r="H1" s="38" t="s">
+      <c r="H1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="16"/>
-      <c r="B2" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
+      <c r="B2" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
       <c r="F2" s="16"/>
       <c r="G2" s="16"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39" t="s">
+      <c r="H2" s="24"/>
+      <c r="I2" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="39" t="s">
+      <c r="J2" s="24" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1367,11 +1557,11 @@
       <c r="E3" s="16"/>
       <c r="F3" s="16"/>
       <c r="G3" s="16"/>
-      <c r="H3" s="39" t="s">
+      <c r="H3" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="16"/>
@@ -1379,44 +1569,44 @@
       <c r="C4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="22"/>
+      <c r="D4" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="32"/>
       <c r="F4" s="16"/>
       <c r="G4" s="16"/>
-      <c r="H4" s="39" t="s">
+      <c r="H4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="16"/>
       <c r="B5" s="16"/>
       <c r="C5" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" s="24"/>
+        <v>37</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="34"/>
       <c r="F5" s="16"/>
       <c r="G5" s="16"/>
-      <c r="H5" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39"/>
+      <c r="H5" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="16"/>
       <c r="B6" s="7"/>
       <c r="C6" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
+        <v>15</v>
+      </c>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
       <c r="F6" s="16"/>
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
@@ -1427,10 +1617,10 @@
       <c r="A7" s="16"/>
       <c r="B7" s="16"/>
       <c r="C7" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
+        <v>16</v>
+      </c>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
       <c r="F7" s="16"/>
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
@@ -1440,16 +1630,16 @@
     <row r="9" spans="1:10">
       <c r="A9" s="16"/>
       <c r="B9" s="9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F9" s="16"/>
       <c r="G9" s="16"/>
@@ -1459,17 +1649,17 @@
     </row>
     <row r="10" spans="1:10" ht="43.5">
       <c r="A10" s="16"/>
-      <c r="B10" s="32">
+      <c r="B10" s="18">
         <v>1</v>
       </c>
-      <c r="C10" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="35" t="s">
-        <v>38</v>
+      <c r="C10" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>41</v>
       </c>
       <c r="F10" s="16"/>
       <c r="G10" s="16"/>
@@ -1479,17 +1669,17 @@
     </row>
     <row r="11" spans="1:10" ht="43.5">
       <c r="A11" s="16"/>
-      <c r="B11" s="34">
+      <c r="B11" s="20">
         <v>2</v>
       </c>
-      <c r="C11" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="35" t="s">
-        <v>41</v>
+      <c r="C11" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>44</v>
       </c>
       <c r="F11" s="16"/>
       <c r="G11" s="16"/>
@@ -1499,17 +1689,17 @@
     </row>
     <row r="12" spans="1:10" ht="83.25">
       <c r="A12" s="16"/>
-      <c r="B12" s="34">
+      <c r="B12" s="20">
         <v>3</v>
       </c>
-      <c r="C12" s="33" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="37" t="s">
-        <v>44</v>
+      <c r="C12" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>47</v>
       </c>
       <c r="F12" s="16"/>
       <c r="G12" s="16"/>
@@ -1519,17 +1709,17 @@
     </row>
     <row r="13" spans="1:10" ht="43.5">
       <c r="A13" s="16"/>
-      <c r="B13" s="34">
+      <c r="B13" s="20">
         <v>4</v>
       </c>
-      <c r="C13" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="E13" s="35" t="s">
-        <v>47</v>
+      <c r="C13" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>50</v>
       </c>
       <c r="F13" s="16"/>
       <c r="G13" s="16"/>
@@ -1539,17 +1729,17 @@
     </row>
     <row r="14" spans="1:10" ht="43.5">
       <c r="A14" s="16"/>
-      <c r="B14" s="34">
+      <c r="B14" s="20">
         <v>5</v>
       </c>
-      <c r="C14" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="E14" s="35" t="s">
-        <v>50</v>
+      <c r="C14" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>53</v>
       </c>
       <c r="F14" s="16"/>
       <c r="G14" s="16"/>
@@ -1559,17 +1749,17 @@
     </row>
     <row r="15" spans="1:10" ht="43.5">
       <c r="A15" s="16"/>
-      <c r="B15" s="34">
+      <c r="B15" s="20">
         <v>6</v>
       </c>
-      <c r="C15" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="35" t="s">
-        <v>52</v>
-      </c>
-      <c r="E15" s="35" t="s">
-        <v>53</v>
+      <c r="C15" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>56</v>
       </c>
       <c r="F15" s="16"/>
       <c r="G15" s="16"/>
@@ -1579,17 +1769,17 @@
     </row>
     <row r="16" spans="1:10" ht="43.5">
       <c r="A16" s="16"/>
-      <c r="B16" s="34">
+      <c r="B16" s="20">
         <v>7</v>
       </c>
-      <c r="C16" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="D16" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="E16" s="35" t="s">
-        <v>56</v>
+      <c r="C16" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>59</v>
       </c>
       <c r="F16" s="16"/>
       <c r="G16" s="16"/>
@@ -1598,49 +1788,49 @@
       <c r="J16" s="16"/>
     </row>
     <row r="17" spans="2:5" ht="29.25">
-      <c r="B17" s="34">
+      <c r="B17" s="20">
         <v>8</v>
       </c>
-      <c r="C17" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="E17" s="35" t="s">
-        <v>58</v>
+      <c r="C17" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="29.25">
-      <c r="B18" s="34">
+      <c r="B18" s="20">
         <v>9</v>
       </c>
-      <c r="C18" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="E18" s="35" t="s">
-        <v>61</v>
+      <c r="C18" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="83.25">
-      <c r="B19" s="34">
+      <c r="B19" s="20">
         <v>10</v>
       </c>
-      <c r="C19" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="D19" s="35" t="s">
-        <v>63</v>
-      </c>
-      <c r="E19" s="37" t="s">
-        <v>64</v>
+      <c r="C19" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19" s="23" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="2:5">
-      <c r="B20" s="39">
+      <c r="B20" s="24">
         <f t="shared" ref="B12:B26" si="0">B19+1</f>
         <v>11</v>
       </c>
@@ -1649,7 +1839,7 @@
       <c r="E20" s="2"/>
     </row>
     <row r="21" spans="2:5">
-      <c r="B21" s="39">
+      <c r="B21" s="24">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -1658,7 +1848,7 @@
       <c r="E21" s="2"/>
     </row>
     <row r="22" spans="2:5">
-      <c r="B22" s="39">
+      <c r="B22" s="24">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
@@ -1667,7 +1857,7 @@
       <c r="E22" s="2"/>
     </row>
     <row r="23" spans="2:5">
-      <c r="B23" s="39">
+      <c r="B23" s="24">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -1676,7 +1866,7 @@
       <c r="E23" s="2"/>
     </row>
     <row r="24" spans="2:5">
-      <c r="B24" s="39">
+      <c r="B24" s="24">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -1685,7 +1875,7 @@
       <c r="E24" s="2"/>
     </row>
     <row r="25" spans="2:5">
-      <c r="B25" s="39">
+      <c r="B25" s="24">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -1694,7 +1884,7 @@
       <c r="E25" s="2"/>
     </row>
     <row r="26" spans="2:5">
-      <c r="B26" s="39">
+      <c r="B26" s="24">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
@@ -1706,12 +1896,12 @@
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
-      <c r="E27" s="31"/>
+      <c r="E27" s="17"/>
     </row>
     <row r="28" spans="2:5">
       <c r="B28" s="16"/>
       <c r="C28" s="10" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D28" s="11"/>
       <c r="E28" s="1"/>
@@ -1758,27 +1948,27 @@
       <c r="E1" s="16"/>
       <c r="F1" s="16"/>
       <c r="G1" s="16"/>
-      <c r="H1" s="38" t="s">
+      <c r="H1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="16"/>
-      <c r="B2" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
+      <c r="B2" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
       <c r="F2" s="16"/>
       <c r="G2" s="16"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39" t="s">
+      <c r="H2" s="24"/>
+      <c r="I2" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="39" t="s">
+      <c r="J2" s="24" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1790,11 +1980,11 @@
       <c r="E3" s="16"/>
       <c r="F3" s="16"/>
       <c r="G3" s="16"/>
-      <c r="H3" s="39" t="s">
+      <c r="H3" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="16"/>
@@ -1802,44 +1992,44 @@
       <c r="C4" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4" s="25"/>
+      <c r="D4" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="35"/>
       <c r="F4" s="16"/>
       <c r="G4" s="16"/>
-      <c r="H4" s="39" t="s">
+      <c r="H4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="16"/>
       <c r="B5" s="16"/>
       <c r="C5" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="E5" s="27"/>
+        <v>11</v>
+      </c>
+      <c r="D5" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="37"/>
       <c r="F5" s="16"/>
       <c r="G5" s="16"/>
-      <c r="H5" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39"/>
+      <c r="H5" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="16"/>
       <c r="B6" s="7"/>
       <c r="C6" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
+        <v>15</v>
+      </c>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
       <c r="F6" s="16"/>
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
@@ -1850,10 +2040,10 @@
       <c r="A7" s="16"/>
       <c r="B7" s="16"/>
       <c r="C7" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
+        <v>16</v>
+      </c>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
       <c r="F7" s="16"/>
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
@@ -1863,16 +2053,16 @@
     <row r="9" spans="1:10">
       <c r="A9" s="16"/>
       <c r="B9" s="9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F9" s="16"/>
       <c r="G9" s="16"/>
@@ -1882,7 +2072,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="16"/>
-      <c r="B10" s="39">
+      <c r="B10" s="24">
         <v>1</v>
       </c>
       <c r="C10" s="1"/>
@@ -1896,7 +2086,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="16"/>
-      <c r="B11" s="39">
+      <c r="B11" s="24">
         <f>B10+1</f>
         <v>2</v>
       </c>
@@ -1911,7 +2101,7 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="16"/>
-      <c r="B12" s="39">
+      <c r="B12" s="24">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
       </c>
@@ -1926,7 +2116,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="16"/>
-      <c r="B13" s="39">
+      <c r="B13" s="24">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -1941,7 +2131,7 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="16"/>
-      <c r="B14" s="39">
+      <c r="B14" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -1956,7 +2146,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="16"/>
-      <c r="B15" s="39">
+      <c r="B15" s="24">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -1971,7 +2161,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="16"/>
-      <c r="B16" s="39">
+      <c r="B16" s="24">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -1985,7 +2175,7 @@
       <c r="J16" s="16"/>
     </row>
     <row r="17" spans="2:5">
-      <c r="B17" s="39">
+      <c r="B17" s="24">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -1994,7 +2184,7 @@
       <c r="E17" s="2"/>
     </row>
     <row r="18" spans="2:5">
-      <c r="B18" s="39">
+      <c r="B18" s="24">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -2003,7 +2193,7 @@
       <c r="E18" s="2"/>
     </row>
     <row r="19" spans="2:5">
-      <c r="B19" s="39">
+      <c r="B19" s="24">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -2012,7 +2202,7 @@
       <c r="E19" s="2"/>
     </row>
     <row r="20" spans="2:5">
-      <c r="B20" s="39">
+      <c r="B20" s="24">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -2021,7 +2211,7 @@
       <c r="E20" s="2"/>
     </row>
     <row r="21" spans="2:5">
-      <c r="B21" s="39">
+      <c r="B21" s="24">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -2030,7 +2220,7 @@
       <c r="E21" s="2"/>
     </row>
     <row r="22" spans="2:5">
-      <c r="B22" s="39">
+      <c r="B22" s="24">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
@@ -2039,7 +2229,7 @@
       <c r="E22" s="2"/>
     </row>
     <row r="23" spans="2:5">
-      <c r="B23" s="39">
+      <c r="B23" s="24">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -2048,7 +2238,7 @@
       <c r="E23" s="2"/>
     </row>
     <row r="24" spans="2:5">
-      <c r="B24" s="39">
+      <c r="B24" s="24">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -2057,7 +2247,7 @@
       <c r="E24" s="2"/>
     </row>
     <row r="25" spans="2:5">
-      <c r="B25" s="39">
+      <c r="B25" s="24">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -2066,7 +2256,7 @@
       <c r="E25" s="2"/>
     </row>
     <row r="26" spans="2:5">
-      <c r="B26" s="39">
+      <c r="B26" s="24">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
@@ -2075,7 +2265,7 @@
       <c r="E26" s="2"/>
     </row>
     <row r="27" spans="2:5">
-      <c r="B27" s="39">
+      <c r="B27" s="24">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
@@ -2084,7 +2274,7 @@
       <c r="E27" s="1"/>
     </row>
     <row r="28" spans="2:5">
-      <c r="B28" s="39">
+      <c r="B28" s="24">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
@@ -2093,7 +2283,7 @@
       <c r="E28" s="2"/>
     </row>
     <row r="29" spans="2:5">
-      <c r="B29" s="39">
+      <c r="B29" s="24">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -2102,7 +2292,7 @@
       <c r="E29" s="2"/>
     </row>
     <row r="30" spans="2:5">
-      <c r="B30" s="39">
+      <c r="B30" s="24">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
@@ -2113,7 +2303,7 @@
     <row r="32" spans="2:5">
       <c r="B32" s="16"/>
       <c r="C32" s="10" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D32" s="11"/>
       <c r="E32" s="1"/>
@@ -2161,27 +2351,27 @@
       <c r="E1" s="16"/>
       <c r="F1" s="16"/>
       <c r="G1" s="16"/>
-      <c r="H1" s="38" t="s">
+      <c r="H1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="16"/>
-      <c r="B2" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
+      <c r="B2" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
       <c r="F2" s="16"/>
       <c r="G2" s="16"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39" t="s">
+      <c r="H2" s="24"/>
+      <c r="I2" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="39" t="s">
+      <c r="J2" s="24" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2193,52 +2383,70 @@
       <c r="E3" s="16"/>
       <c r="F3" s="16"/>
       <c r="G3" s="16"/>
-      <c r="H3" s="39" t="s">
+      <c r="H3" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
+      <c r="I3" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="24">
+        <v>237</v>
+      </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="16"/>
       <c r="B4" s="16"/>
       <c r="C4" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
+        <v>72</v>
+      </c>
+      <c r="D4" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="35"/>
       <c r="F4" s="16"/>
       <c r="G4" s="16"/>
-      <c r="H4" s="39" t="s">
+      <c r="H4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
+      <c r="I4" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="24">
+        <v>237</v>
+      </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="16"/>
       <c r="B5" s="16"/>
       <c r="C5" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
+        <v>15</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="26"/>
       <c r="F5" s="16"/>
       <c r="G5" s="16"/>
-      <c r="H5" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39"/>
+      <c r="H5" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="24">
+        <v>237</v>
+      </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="16"/>
       <c r="B6" s="7"/>
       <c r="C6" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
+        <v>16</v>
+      </c>
+      <c r="D6" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="26"/>
       <c r="F6" s="16"/>
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
@@ -2248,32 +2456,36 @@
     <row r="9" spans="1:10">
       <c r="A9" s="16"/>
       <c r="B9" s="9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
       <c r="I9" s="16"/>
       <c r="J9" s="16"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" ht="45.75">
       <c r="A10" s="16"/>
-      <c r="B10" s="39">
+      <c r="B10" s="24">
         <v>1</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="2"/>
+      <c r="C10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="16"/>
@@ -2281,61 +2493,91 @@
       <c r="I10" s="16"/>
       <c r="J10" s="16"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="91.5">
       <c r="A11" s="16"/>
-      <c r="B11" s="39">
+      <c r="B11" s="24">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
+      <c r="C11" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>83</v>
+      </c>
       <c r="G11" s="16"/>
       <c r="H11" s="16"/>
       <c r="I11" s="16"/>
       <c r="J11" s="16"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="137.25">
       <c r="A12" s="16"/>
-      <c r="B12" s="39">
+      <c r="B12" s="24">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
+      <c r="C12" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
       <c r="I12" s="16"/>
       <c r="J12" s="16"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="106.5">
       <c r="A13" s="16"/>
-      <c r="B13" s="39">
+      <c r="B13" s="24">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="C13" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="F13" s="2"/>
       <c r="G13" s="16"/>
       <c r="H13" s="16"/>
       <c r="I13" s="16"/>
       <c r="J13" s="16"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="305.25">
       <c r="A14" s="16"/>
-      <c r="B14" s="39">
+      <c r="B14" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
+      <c r="C14" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>93</v>
+      </c>
       <c r="G14" s="16"/>
       <c r="H14" s="16"/>
       <c r="I14" s="16"/>
@@ -2343,7 +2585,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="16"/>
-      <c r="B15" s="39">
+      <c r="B15" s="24">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -2358,7 +2600,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="16"/>
-      <c r="B16" s="39">
+      <c r="B16" s="24">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -2372,7 +2614,7 @@
       <c r="J16" s="16"/>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="39">
+      <c r="B17" s="24">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -2382,7 +2624,7 @@
       <c r="F17" s="2"/>
     </row>
     <row r="18" spans="2:6">
-      <c r="B18" s="39">
+      <c r="B18" s="24">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -2392,7 +2634,7 @@
       <c r="F18" s="2"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="B19" s="39">
+      <c r="B19" s="24">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -2402,7 +2644,7 @@
       <c r="F19" s="2"/>
     </row>
     <row r="20" spans="2:6">
-      <c r="B20" s="39">
+      <c r="B20" s="24">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -2412,7 +2654,7 @@
       <c r="F20" s="2"/>
     </row>
     <row r="21" spans="2:6">
-      <c r="B21" s="39">
+      <c r="B21" s="24">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -2422,7 +2664,7 @@
       <c r="F21" s="2"/>
     </row>
     <row r="22" spans="2:6">
-      <c r="B22" s="39">
+      <c r="B22" s="24">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
@@ -2432,7 +2674,7 @@
       <c r="F22" s="2"/>
     </row>
     <row r="23" spans="2:6">
-      <c r="B23" s="39">
+      <c r="B23" s="24">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -2442,7 +2684,7 @@
       <c r="F23" s="2"/>
     </row>
     <row r="24" spans="2:6">
-      <c r="B24" s="39">
+      <c r="B24" s="24">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -2452,7 +2694,7 @@
       <c r="F24" s="2"/>
     </row>
     <row r="25" spans="2:6">
-      <c r="B25" s="39">
+      <c r="B25" s="24">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -2462,7 +2704,7 @@
       <c r="F25" s="2"/>
     </row>
     <row r="26" spans="2:6">
-      <c r="B26" s="39">
+      <c r="B26" s="24">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
@@ -2472,7 +2714,7 @@
       <c r="F26" s="2"/>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="39">
+      <c r="B27" s="24">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
@@ -2482,7 +2724,7 @@
       <c r="F27" s="1"/>
     </row>
     <row r="28" spans="2:6">
-      <c r="B28" s="39">
+      <c r="B28" s="24">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
@@ -2492,7 +2734,7 @@
       <c r="F28" s="2"/>
     </row>
     <row r="29" spans="2:6">
-      <c r="B29" s="39">
+      <c r="B29" s="24">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -2502,7 +2744,7 @@
       <c r="F29" s="2"/>
     </row>
     <row r="30" spans="2:6">
-      <c r="B30" s="39">
+      <c r="B30" s="24">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
@@ -2513,11 +2755,11 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="16"/>
-      <c r="C32" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
+      <c r="C32" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="D32" s="39"/>
+      <c r="E32" s="39"/>
       <c r="F32" s="15"/>
     </row>
     <row r="35" spans="6:6">
@@ -2534,5 +2776,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29910"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Laptop\e\VVSS\CamiVVSS_ro2025-2026\Labs\CheckListsAll\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\calin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="122" documentId="13_ncr:1_{EFE83867-3721-469D-B0A3-67FDA22FF09F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAD67BE2-A3EB-49C8-95C1-F2675151D60C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD255739-18E4-4FE7-8097-606767D92514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="650" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="109">
   <si>
     <t>do not print this form</t>
   </si>
@@ -298,6 +298,45 @@
     <t>Popescu Ionel</t>
   </si>
   <si>
+    <t>Ursoiu Călin-Alexandru</t>
+  </si>
+  <si>
+    <t>C01</t>
+  </si>
+  <si>
+    <t>OrderService.java</t>
+  </si>
+  <si>
+    <t>computeTotal a fost făcut null‑safe și cu fallback de preț (dacă produsul nu mai există în repo), ca să nu dea crash la findOne(...).getPret() și să definească explicit regula de calcul a totalului.</t>
+  </si>
+  <si>
+    <t>StocService.java</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S-a introdus verificarea/consumul de stoc pe un “coș” agregat </t>
+  </si>
+  <si>
+    <t>DrinkShopService.java/DrinkShopController.java</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In DrinkShopService s-a adăugat finalizeazaComanda(Order) care calculează necesarul total de ingrediente din rețete × cantități, consumă stocul și abia apoi salvează comanda.  Iar in DrinkShopController </t>
+  </si>
+  <si>
+    <t>C04</t>
+  </si>
+  <si>
+    <t>FileStocRepository.java</t>
+  </si>
+  <si>
+    <t>Eroare de format I/O: fișierul stocuri.txt ajunge să conțină 1000.0, dar citirea era pe int. Îmbunătățire: se parsează cu Double.parseDouble(...) și la scriere se formatează să nu apară .0 când valoarea e întreagă.</t>
+  </si>
+  <si>
+    <t>C02</t>
+  </si>
+  <si>
+    <t>Branching greșit în comandaProdus: după retetaService.findById(produs.getId()) nu exista ramură pentru cazul reteta == null, ceea ce putea produce NullPointerException la verificarea/consumul de stoc.  Îmbunătățire: s-a adăugat if (reteta == null) throw ... (și if (produs == null) throw ...), apoi se consumă stocul doar dacă există rețetă.</t>
+  </si>
+  <si>
     <t>Tool-based Code Analysis</t>
   </si>
   <si>
@@ -386,12 +425,15 @@
   <si>
     <t>Effort to perform tool-based code analysis (hours): 1</t>
   </si>
+  <si>
+    <t>Vițelaru Teodor</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -491,6 +533,33 @@
       <sz val="10"/>
       <color rgb="FF928374"/>
       <name val="Segoe WPC"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -603,10 +672,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -649,14 +719,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -676,15 +762,6 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -695,7 +772,8 @@
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1101,19 +1179,19 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="5"/>
-    <col min="2" max="2" width="12.28515625" style="5" customWidth="1"/>
-    <col min="3" max="4" width="16.28515625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="41.42578125" style="5" customWidth="1"/>
-    <col min="6" max="8" width="8.85546875" style="5"/>
+    <col min="1" max="1" width="8.81640625" style="5"/>
+    <col min="2" max="2" width="12.26953125" style="5" customWidth="1"/>
+    <col min="3" max="4" width="16.26953125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="41.453125" style="5" customWidth="1"/>
+    <col min="6" max="8" width="8.81640625" style="5"/>
     <col min="9" max="9" width="21" style="5" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="5" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="5"/>
+    <col min="10" max="10" width="14.453125" style="5" customWidth="1"/>
+    <col min="11" max="16384" width="8.81640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.6">
+    <row r="1" spans="1:10" ht="15.5">
       <c r="A1" s="3"/>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -1123,20 +1201,20 @@
       <c r="E1" s="16"/>
       <c r="F1" s="16"/>
       <c r="G1" s="16"/>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="16"/>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
       <c r="F2" s="16"/>
       <c r="G2" s="16"/>
       <c r="H2" s="24"/>
@@ -1171,10 +1249,10 @@
       <c r="C4" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="29"/>
+      <c r="E4" s="35"/>
       <c r="F4" s="16"/>
       <c r="G4" s="16"/>
       <c r="H4" s="24" t="s">
@@ -1193,10 +1271,10 @@
       <c r="C5" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="31"/>
+      <c r="E5" s="37"/>
       <c r="F5" s="16"/>
       <c r="G5" s="16"/>
       <c r="H5" s="24" t="s">
@@ -1215,10 +1293,10 @@
       <c r="C6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="26"/>
+      <c r="E6" s="29"/>
       <c r="F6" s="16"/>
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
@@ -1231,10 +1309,10 @@
       <c r="C7" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="26"/>
+      <c r="E7" s="29"/>
       <c r="F7" s="16"/>
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
@@ -1261,7 +1339,7 @@
       <c r="I9" s="16"/>
       <c r="J9" s="16"/>
     </row>
-    <row r="10" spans="1:10" ht="30.75">
+    <row r="10" spans="1:10" ht="29">
       <c r="A10" s="16"/>
       <c r="B10" s="24">
         <v>1</v>
@@ -1281,7 +1359,7 @@
       <c r="I10" s="16"/>
       <c r="J10" s="16"/>
     </row>
-    <row r="11" spans="1:10" ht="30.75">
+    <row r="11" spans="1:10" ht="29">
       <c r="A11" s="16"/>
       <c r="B11" s="24">
         <f>B10+1</f>
@@ -1302,7 +1380,7 @@
       <c r="I11" s="16"/>
       <c r="J11" s="16"/>
     </row>
-    <row r="12" spans="1:10" ht="45.75">
+    <row r="12" spans="1:10" ht="43.5">
       <c r="A12" s="16"/>
       <c r="B12" s="24">
         <f t="shared" ref="B12:B25" si="0">B11+1</f>
@@ -1323,7 +1401,7 @@
       <c r="I12" s="16"/>
       <c r="J12" s="16"/>
     </row>
-    <row r="13" spans="1:10" ht="45.75">
+    <row r="13" spans="1:10" ht="43.5">
       <c r="A13" s="16"/>
       <c r="B13" s="24">
         <f t="shared" si="0"/>
@@ -1344,7 +1422,7 @@
       <c r="I13" s="16"/>
       <c r="J13" s="16"/>
     </row>
-    <row r="14" spans="1:10" ht="45.75">
+    <row r="14" spans="1:10" ht="43.5">
       <c r="A14" s="16"/>
       <c r="B14" s="24">
         <f t="shared" si="0"/>
@@ -1504,18 +1582,18 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J28"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="5"/>
-    <col min="2" max="2" width="12.28515625" style="5" customWidth="1"/>
-    <col min="3" max="4" width="16.28515625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="41.42578125" style="5" customWidth="1"/>
-    <col min="6" max="8" width="8.85546875" style="5"/>
-    <col min="9" max="9" width="22.140625" style="5" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="5"/>
+    <col min="1" max="1" width="8.81640625" style="5"/>
+    <col min="2" max="2" width="12.26953125" style="5" customWidth="1"/>
+    <col min="3" max="4" width="16.26953125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="41.453125" style="5" customWidth="1"/>
+    <col min="6" max="8" width="8.81640625" style="5"/>
+    <col min="9" max="9" width="22.1796875" style="5" customWidth="1"/>
+    <col min="10" max="16384" width="8.81640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.6">
+    <row r="1" spans="1:10" ht="15.5">
       <c r="A1" s="3"/>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -1525,20 +1603,20 @@
       <c r="E1" s="16"/>
       <c r="F1" s="16"/>
       <c r="G1" s="16"/>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="16"/>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
       <c r="F2" s="16"/>
       <c r="G2" s="16"/>
       <c r="H2" s="24"/>
@@ -1569,10 +1647,10 @@
       <c r="C4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="32"/>
+      <c r="E4" s="38"/>
       <c r="F4" s="16"/>
       <c r="G4" s="16"/>
       <c r="H4" s="24" t="s">
@@ -1587,10 +1665,10 @@
       <c r="C5" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="34"/>
+      <c r="E5" s="40"/>
       <c r="F5" s="16"/>
       <c r="G5" s="16"/>
       <c r="H5" s="24" t="s">
@@ -1605,8 +1683,10 @@
       <c r="C6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
+      <c r="D6" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="E6" s="29"/>
       <c r="F6" s="16"/>
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
@@ -1619,8 +1699,8 @@
       <c r="C7" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
       <c r="F7" s="16"/>
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
@@ -1647,7 +1727,7 @@
       <c r="I9" s="16"/>
       <c r="J9" s="16"/>
     </row>
-    <row r="10" spans="1:10" ht="43.5">
+    <row r="10" spans="1:10" ht="48">
       <c r="A10" s="16"/>
       <c r="B10" s="18">
         <v>1</v>
@@ -1667,7 +1747,7 @@
       <c r="I10" s="16"/>
       <c r="J10" s="16"/>
     </row>
-    <row r="11" spans="1:10" ht="43.5">
+    <row r="11" spans="1:10" ht="48">
       <c r="A11" s="16"/>
       <c r="B11" s="20">
         <v>2</v>
@@ -1687,7 +1767,7 @@
       <c r="I11" s="16"/>
       <c r="J11" s="16"/>
     </row>
-    <row r="12" spans="1:10" ht="83.25">
+    <row r="12" spans="1:10" ht="77">
       <c r="A12" s="16"/>
       <c r="B12" s="20">
         <v>3</v>
@@ -1707,7 +1787,7 @@
       <c r="I12" s="16"/>
       <c r="J12" s="16"/>
     </row>
-    <row r="13" spans="1:10" ht="43.5">
+    <row r="13" spans="1:10" ht="48">
       <c r="A13" s="16"/>
       <c r="B13" s="20">
         <v>4</v>
@@ -1727,7 +1807,7 @@
       <c r="I13" s="16"/>
       <c r="J13" s="16"/>
     </row>
-    <row r="14" spans="1:10" ht="43.5">
+    <row r="14" spans="1:10" ht="48">
       <c r="A14" s="16"/>
       <c r="B14" s="20">
         <v>5</v>
@@ -1747,7 +1827,7 @@
       <c r="I14" s="16"/>
       <c r="J14" s="16"/>
     </row>
-    <row r="15" spans="1:10" ht="43.5">
+    <row r="15" spans="1:10" ht="48">
       <c r="A15" s="16"/>
       <c r="B15" s="20">
         <v>6</v>
@@ -1767,7 +1847,7 @@
       <c r="I15" s="16"/>
       <c r="J15" s="16"/>
     </row>
-    <row r="16" spans="1:10" ht="43.5">
+    <row r="16" spans="1:10" ht="48">
       <c r="A16" s="16"/>
       <c r="B16" s="20">
         <v>7</v>
@@ -1787,7 +1867,7 @@
       <c r="I16" s="16"/>
       <c r="J16" s="16"/>
     </row>
-    <row r="17" spans="2:5" ht="29.25">
+    <row r="17" spans="2:5" ht="32">
       <c r="B17" s="20">
         <v>8</v>
       </c>
@@ -1801,7 +1881,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="29.25">
+    <row r="18" spans="2:5" ht="32">
       <c r="B18" s="20">
         <v>9</v>
       </c>
@@ -1815,7 +1895,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="83.25">
+    <row r="19" spans="2:5" ht="77">
       <c r="B19" s="20">
         <v>10</v>
       </c>
@@ -1831,7 +1911,7 @@
     </row>
     <row r="20" spans="2:5">
       <c r="B20" s="24">
-        <f t="shared" ref="B12:B26" si="0">B19+1</f>
+        <f t="shared" ref="B20:B26" si="0">B19+1</f>
         <v>11</v>
       </c>
       <c r="C20" s="1"/>
@@ -1892,7 +1972,7 @@
       <c r="D26" s="1"/>
       <c r="E26" s="2"/>
     </row>
-    <row r="27" spans="2:5" ht="15">
+    <row r="27" spans="2:5">
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
@@ -1904,7 +1984,9 @@
         <v>34</v>
       </c>
       <c r="D28" s="11"/>
-      <c r="E28" s="1"/>
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1926,19 +2008,19 @@
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="5"/>
-    <col min="2" max="2" width="12.28515625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" style="5"/>
+    <col min="2" max="2" width="12.26953125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="16.26953125" style="5" customWidth="1"/>
     <col min="4" max="4" width="18" style="5" customWidth="1"/>
-    <col min="5" max="5" width="41.42578125" style="5" customWidth="1"/>
-    <col min="6" max="8" width="8.85546875" style="5"/>
-    <col min="9" max="9" width="26.7109375" style="5" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="5"/>
+    <col min="5" max="5" width="41.453125" style="5" customWidth="1"/>
+    <col min="6" max="8" width="8.81640625" style="5"/>
+    <col min="9" max="9" width="26.7265625" style="5" customWidth="1"/>
+    <col min="10" max="16384" width="8.81640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.6">
+    <row r="1" spans="1:10" ht="15.5">
       <c r="A1" s="3"/>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -1948,20 +2030,20 @@
       <c r="E1" s="16"/>
       <c r="F1" s="16"/>
       <c r="G1" s="16"/>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="16"/>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
       <c r="F2" s="16"/>
       <c r="G2" s="16"/>
       <c r="H2" s="24"/>
@@ -1983,8 +2065,12 @@
       <c r="H3" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
+      <c r="I3" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="24">
+        <v>237</v>
+      </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="16"/>
@@ -1992,17 +2078,21 @@
       <c r="C4" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="D4" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="E4" s="35"/>
+      <c r="E4" s="31"/>
       <c r="F4" s="16"/>
       <c r="G4" s="16"/>
       <c r="H4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
+      <c r="I4" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="24">
+        <v>237</v>
+      </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="16"/>
@@ -2010,17 +2100,21 @@
       <c r="C5" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="36" t="s">
+      <c r="D5" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="37"/>
+      <c r="E5" s="34"/>
       <c r="F5" s="16"/>
       <c r="G5" s="16"/>
       <c r="H5" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24"/>
+      <c r="I5" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="24">
+        <v>237</v>
+      </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="16"/>
@@ -2028,8 +2122,10 @@
       <c r="C6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
+      <c r="D6" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="29"/>
       <c r="F6" s="16"/>
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
@@ -2042,8 +2138,8 @@
       <c r="C7" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
       <c r="F7" s="16"/>
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
@@ -2070,74 +2166,104 @@
       <c r="I9" s="16"/>
       <c r="J9" s="16"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" ht="58">
       <c r="A10" s="16"/>
       <c r="B10" s="24">
         <v>1</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
+      <c r="C10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="F10" s="16"/>
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>
       <c r="I10" s="16"/>
       <c r="J10" s="16"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="29">
       <c r="A11" s="16"/>
       <c r="B11" s="24">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="2"/>
+      <c r="C11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="F11" s="16"/>
       <c r="G11" s="16"/>
       <c r="H11" s="16"/>
       <c r="I11" s="16"/>
       <c r="J11" s="16"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="72.5">
       <c r="A12" s="16"/>
       <c r="B12" s="24">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
+      <c r="C12" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>78</v>
+      </c>
       <c r="F12" s="16"/>
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
       <c r="I12" s="16"/>
       <c r="J12" s="16"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="87">
       <c r="A13" s="16"/>
       <c r="B13" s="24">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="C13" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>81</v>
+      </c>
       <c r="F13" s="16"/>
       <c r="G13" s="16"/>
       <c r="H13" s="16"/>
       <c r="I13" s="16"/>
       <c r="J13" s="16"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="116">
       <c r="A14" s="16"/>
       <c r="B14" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
+      <c r="C14" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>83</v>
+      </c>
       <c r="F14" s="16"/>
       <c r="G14" s="16"/>
       <c r="H14" s="16"/>
@@ -2306,7 +2432,9 @@
         <v>34</v>
       </c>
       <c r="D32" s="11"/>
-      <c r="E32" s="1"/>
+      <c r="E32" s="1">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2328,20 +2456,20 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:J35"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="5"/>
-    <col min="2" max="2" width="12.28515625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" style="5"/>
+    <col min="2" max="2" width="12.26953125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="16.26953125" style="5" customWidth="1"/>
     <col min="4" max="4" width="18" style="5" customWidth="1"/>
-    <col min="5" max="5" width="23.85546875" style="5" customWidth="1"/>
-    <col min="6" max="6" width="16.5703125" style="5" customWidth="1"/>
-    <col min="7" max="8" width="8.85546875" style="5"/>
-    <col min="9" max="9" width="26.7109375" style="5" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="5"/>
+    <col min="5" max="5" width="23.81640625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="16.54296875" style="5" customWidth="1"/>
+    <col min="7" max="8" width="8.81640625" style="5"/>
+    <col min="9" max="9" width="26.7265625" style="5" customWidth="1"/>
+    <col min="10" max="16384" width="8.81640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.6">
+    <row r="1" spans="1:10" ht="15.5">
       <c r="A1" s="3"/>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -2351,20 +2479,20 @@
       <c r="E1" s="16"/>
       <c r="F1" s="16"/>
       <c r="G1" s="16"/>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="16"/>
-      <c r="B2" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
+      <c r="B2" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
       <c r="F2" s="16"/>
       <c r="G2" s="16"/>
       <c r="H2" s="24"/>
@@ -2397,12 +2525,12 @@
       <c r="A4" s="16"/>
       <c r="B4" s="16"/>
       <c r="C4" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="D4" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="E4" s="35"/>
+        <v>85</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="31"/>
       <c r="F4" s="16"/>
       <c r="G4" s="16"/>
       <c r="H4" s="24" t="s">
@@ -2421,10 +2549,10 @@
       <c r="C5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="26"/>
+      <c r="E5" s="29"/>
       <c r="F5" s="16"/>
       <c r="G5" s="16"/>
       <c r="H5" s="24" t="s">
@@ -2443,10 +2571,10 @@
       <c r="C6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="40" t="s">
+      <c r="D6" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="26"/>
+      <c r="E6" s="29"/>
       <c r="F6" s="16"/>
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
@@ -2459,32 +2587,32 @@
         <v>18</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
       <c r="I9" s="16"/>
       <c r="J9" s="16"/>
     </row>
-    <row r="10" spans="1:10" ht="45.75">
+    <row r="10" spans="1:10" ht="43.5">
       <c r="A10" s="16"/>
       <c r="B10" s="24">
         <v>1</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -2493,66 +2621,66 @@
       <c r="I10" s="16"/>
       <c r="J10" s="16"/>
     </row>
-    <row r="11" spans="1:10" ht="91.5">
+    <row r="11" spans="1:10" ht="87">
       <c r="A11" s="16"/>
       <c r="B11" s="24">
         <f>B10+1</f>
         <v>2</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="G11" s="16"/>
       <c r="H11" s="16"/>
       <c r="I11" s="16"/>
       <c r="J11" s="16"/>
     </row>
-    <row r="12" spans="1:10" ht="137.25">
+    <row r="12" spans="1:10" ht="130.5">
       <c r="A12" s="16"/>
       <c r="B12" s="24">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
       <c r="I12" s="16"/>
       <c r="J12" s="16"/>
     </row>
-    <row r="13" spans="1:10" ht="106.5">
+    <row r="13" spans="1:10" ht="87">
       <c r="A13" s="16"/>
       <c r="B13" s="24">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="16"/>
@@ -2560,23 +2688,23 @@
       <c r="I13" s="16"/>
       <c r="J13" s="16"/>
     </row>
-    <row r="14" spans="1:10" ht="305.25">
+    <row r="14" spans="1:10" ht="290">
       <c r="A14" s="16"/>
       <c r="B14" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="G14" s="16"/>
       <c r="H14" s="16"/>
@@ -2755,11 +2883,11 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="16"/>
-      <c r="C32" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
+      <c r="C32" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="D32" s="42"/>
+      <c r="E32" s="42"/>
       <c r="F32" s="15"/>
     </row>
     <row r="35" spans="6:6">
